--- a/deliverables/Enterprise_Peaker_Model.xlsx
+++ b/deliverables/Enterprise_Peaker_Model.xlsx
@@ -3237,6 +3237,10 @@
           <t>$</t>
         </is>
       </c>
+      <c r="D84" s="9">
+        <f>D80</f>
+        <v/>
+      </c>
       <c r="E84" s="9">
         <f>MAX(0,E80-E82)</f>
         <v/>
@@ -3951,6 +3955,10 @@
           <t>$</t>
         </is>
       </c>
+      <c r="D97" s="9">
+        <f>D93</f>
+        <v/>
+      </c>
       <c r="E97" s="9">
         <f>MAX(0,E93-E95)</f>
         <v/>
@@ -4835,7 +4843,7 @@
         </is>
       </c>
       <c r="D142" s="22">
-        <f>IF($D$102&gt;=1.4,"PASS","FAIL")</f>
+        <f>IF(ROUND($D$102,4)&gt;=1.4,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -4846,7 +4854,7 @@
         </is>
       </c>
       <c r="D143" s="22">
-        <f>IF(E57=1,"PASS","FAIL")</f>
+        <f>IF(ROUND(E57,4)=1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
